--- a/backend/resources/templates/cs-form-6.xlsx
+++ b/backend/resources/templates/cs-form-6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\ENHS-Leave-Management-System\backend\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535FD2B8-9BFF-4FFC-9555-B79811DB89FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C636A7C-D305-48AE-B07D-A4CAE7FFF335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t>APPLICATION FOR LEAVE</t>
   </si>
@@ -462,9 +462,6 @@
   </si>
   <si>
     <t>2.  NAME :                    (Last)                                   (First)                         (Middle)</t>
-  </si>
-  <si>
-    <t>School Principal II</t>
   </si>
 </sst>
 </file>
@@ -1006,6 +1003,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1053,18 +1062,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3256,15 +3253,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1804572</xdr:colOff>
+      <xdr:colOff>1920458</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>95230</xdr:rowOff>
+      <xdr:rowOff>79687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2503675</xdr:colOff>
+      <xdr:colOff>2619561</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>293667</xdr:rowOff>
+      <xdr:rowOff>278124</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3279,7 +3276,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6275490" y="2252934"/>
+          <a:off x="6378609" y="2241129"/>
           <a:ext cx="699103" cy="198437"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4343,20 +4340,6 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>EMILY O.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> BENITEZ</a:t>
-          </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="1">
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -4847,10 +4830,10 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>762000</xdr:colOff>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
           <xdr:row>61</xdr:row>
-          <xdr:rowOff>123825</xdr:rowOff>
+          <xdr:rowOff>152400</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5180,45 +5163,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
       <c r="I1" s="49"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
       <c r="N2" s="43"/>
     </row>
     <row r="3" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
       <c r="J3" s="1"/>
       <c r="N3" s="43"/>
     </row>
@@ -5242,14 +5225,14 @@
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="69"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="73"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5281,16 +5264,16 @@
     </row>
     <row r="8" spans="1:14" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="65"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
       <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -5619,12 +5602,12 @@
     <row r="31" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="56"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60"/>
       <c r="G31" s="2"/>
       <c r="H31" s="29" t="s">
         <v>20</v>
@@ -5879,25 +5862,25 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="66" t="s">
+      <c r="G49" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="62"/>
-      <c r="I49" s="63"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="35"/>
-      <c r="B50" s="64" t="s">
+      <c r="B50" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
-      <c r="E50" s="64"/>
-      <c r="F50" s="64"/>
-      <c r="G50" s="64"/>
-      <c r="H50" s="64"/>
-      <c r="I50" s="65"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="69"/>
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="1:10" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -6038,17 +6021,15 @@
     <row r="60" spans="1:10" s="42" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="38"/>
       <c r="B60" s="39"/>
-      <c r="C60" s="60" t="s">
+      <c r="C60" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="60"/>
-      <c r="E60" s="60"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="64"/>
       <c r="F60" s="40"/>
-      <c r="G60" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="H60" s="62"/>
-      <c r="I60" s="63"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="67"/>
       <c r="J60" s="41"/>
     </row>
     <row r="61" spans="1:10" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -6113,17 +6094,17 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="70" t="s">
+      <c r="A65" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="71"/>
-      <c r="C65" s="71"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="71"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="71"/>
-      <c r="H65" s="71"/>
-      <c r="I65" s="72"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="56"/>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="52"/>
@@ -6137,68 +6118,62 @@
       <c r="I66" s="53"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="73"/>
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="73"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="73"/>
+      <c r="A67" s="57"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
     </row>
     <row r="68" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="73"/>
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="73"/>
-      <c r="H68" s="73"/>
-      <c r="I68" s="73"/>
+      <c r="A68" s="57"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
     </row>
     <row r="69" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="73"/>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="73"/>
+      <c r="A69" s="57"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="57"/>
     </row>
     <row r="70" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="73"/>
-      <c r="B70" s="73"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="73"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
-      <c r="G70" s="73"/>
-      <c r="H70" s="73"/>
-      <c r="I70" s="73"/>
+      <c r="A70" s="57"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
     </row>
     <row r="71" spans="1:9" s="28" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="73"/>
-      <c r="B71" s="73"/>
-      <c r="C71" s="73"/>
-      <c r="D71" s="73"/>
-      <c r="E71" s="73"/>
-      <c r="F71" s="73"/>
-      <c r="G71" s="73"/>
-      <c r="H71" s="73"/>
-      <c r="I71" s="73"/>
+      <c r="A71" s="57"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A70:I70"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="A2:I2"/>
@@ -6210,6 +6185,12 @@
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="E5:I5"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A70:I70"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0" header="0.5" footer="0.5"/>
@@ -6803,10 +6784,10 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>762000</xdr:colOff>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
                 <xdr:row>61</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
+                <xdr:rowOff>152400</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
